--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:38</t>
+    <t xml:space="preserve">2026-09-09 22:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:24</t>
+    <t xml:space="preserve">2026-09-12 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
@@ -51,12 +51,12 @@
     <t xml:space="preserve">Guaitecas</t>
   </si>
   <si>
+    <t xml:space="preserve">Cochrane</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cisnes</t>
   </si>
   <si>
-    <t xml:space="preserve">Cochrane</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chile Chico</t>
   </si>
   <si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:40</t>
+    <t xml:space="preserve">2026-09-24 00:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>112.85</v>
+        <v>64.23</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>63.44</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>53.77</v>
+        <v>29.08</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>53.51</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>48.44</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="7">
@@ -587,13 +587,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>11202</v>
+        <v>11301</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>44.58</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="8">
@@ -604,13 +604,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>11301</v>
+        <v>11202</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>43.29</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>38.79</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>30.17</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +661,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>25.92</v>
+        <v>11.56</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:18</t>
+    <t xml:space="preserve">2026-09-27 22:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:07</t>
+    <t xml:space="preserve">2026-09-29 11:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>64.23</v>
+        <v>642.34</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32.7</v>
+        <v>327.03</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>29.08</v>
+        <v>290.78</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>27.49</v>
+        <v>274.95</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>22.06</v>
+        <v>220.61</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>21.24</v>
+        <v>212.41</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19.86</v>
+        <v>198.62</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>18.18</v>
+        <v>181.78</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14.73</v>
+        <v>147.29</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +661,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11.56</v>
+        <v>115.56</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:01</t>
+    <t xml:space="preserve">2026-10-01 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:26</t>
+    <t xml:space="preserve">2026-10-02 13:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:10</t>
+    <t xml:space="preserve">2026-10-04 07:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 07:58</t>
+    <t xml:space="preserve">2026-10-05 07:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
